--- a/reports/company/Hengli_SSE601100/Hengli_SSE601100_Financial_Model_2026-05-19.xlsx
+++ b/reports/company/Hengli_SSE601100/Hengli_SSE601100_Financial_Model_2026-05-19.xlsx
@@ -14,6 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF Inputs" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparables" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation Summary" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,11 +26,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="#,##0.0;(#,##0.0);—"/>
     <numFmt numFmtId="165" formatCode="0.0%;(0.0%);—"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="0.0&quot;×&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,8 +85,23 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -114,6 +138,16 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -132,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -177,6 +211,43 @@
     <xf numFmtId="165" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="12" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="12" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -544,7 +615,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
@@ -762,6 +833,1321 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>COMPARABLE COMPANIES ANALYSIS — Hydraulics &amp; Linear-Motion peers</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="46" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B3" s="46" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C3" s="46" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="D3" s="46" t="inlineStr">
+        <is>
+          <t>MarketCap (RMB bn)</t>
+        </is>
+      </c>
+      <c r="E3" s="46" t="inlineStr">
+        <is>
+          <t>TTM Rev (RMB bn)</t>
+        </is>
+      </c>
+      <c r="F3" s="46" t="inlineStr">
+        <is>
+          <t>TTM EBITDA (RMB bn)</t>
+        </is>
+      </c>
+      <c r="G3" s="46" t="inlineStr">
+        <is>
+          <t>TTM NI (RMB bn)</t>
+        </is>
+      </c>
+      <c r="H3" s="46" t="inlineStr">
+        <is>
+          <t>TTM P/E (×)</t>
+        </is>
+      </c>
+      <c r="I3" s="46" t="inlineStr">
+        <is>
+          <t>EV/EBITDA (×)</t>
+        </is>
+      </c>
+      <c r="J3" s="46" t="inlineStr">
+        <is>
+          <t>P/S (×)</t>
+        </is>
+      </c>
+      <c r="K3" s="46" t="inlineStr">
+        <is>
+          <t>P/B (×)</t>
+        </is>
+      </c>
+      <c r="L3" s="46" t="inlineStr">
+        <is>
+          <t>ROE (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Hengli Hydraulics</t>
+        </is>
+      </c>
+      <c r="B4" s="47" t="inlineStr">
+        <is>
+          <t>SSE:601100</t>
+        </is>
+      </c>
+      <c r="C4" s="47" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D4" s="48" t="n">
+        <v>160</v>
+      </c>
+      <c r="E4" s="48" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="F4" s="48" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="G4" s="48" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H4" s="49" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="I4" s="49" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="J4" s="49" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="K4" s="49" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="L4" s="50" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="51" t="inlineStr">
+        <is>
+          <t>Yantai Eddie Precision</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>SSE:603638</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D5" s="52" t="n">
+        <v>19</v>
+      </c>
+      <c r="E5" s="52" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F5" s="52" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G5" s="52" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H5" s="53" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="I5" s="53" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="J5" s="53" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K5" s="53" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L5" s="54" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="51" t="inlineStr">
+        <is>
+          <t>KYB Corporation</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>TYO:7242</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D6" s="52" t="n">
+        <v>29</v>
+      </c>
+      <c r="E6" s="52" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="F6" s="52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G6" s="52" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H6" s="53" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="I6" s="53" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="J6" s="53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="53" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L6" s="54" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="51" t="inlineStr">
+        <is>
+          <t>Parker Hannifin</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>NYSE:PH</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D7" s="52" t="n">
+        <v>1280</v>
+      </c>
+      <c r="E7" s="52" t="n">
+        <v>141.3</v>
+      </c>
+      <c r="F7" s="52" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="G7" s="52" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="H7" s="53" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="I7" s="53" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="J7" s="53" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="K7" s="53" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L7" s="54" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="51" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>NYSE:ETN</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D8" s="52" t="n">
+        <v>1140</v>
+      </c>
+      <c r="E8" s="52" t="n">
+        <v>193.2</v>
+      </c>
+      <c r="F8" s="52" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="G8" s="52" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="H8" s="53" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="I8" s="53" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="J8" s="53" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K8" s="53" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L8" s="54" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="51" t="inlineStr">
+        <is>
+          <t>Schaeffler</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>ETR:SHA</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="D9" s="52" t="n">
+        <v>85</v>
+      </c>
+      <c r="E9" s="52" t="n">
+        <v>127.4</v>
+      </c>
+      <c r="F9" s="52" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G9" s="52" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H9" s="53" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="I9" s="53" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J9" s="53" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K9" s="53" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L9" s="54" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="51" t="inlineStr">
+        <is>
+          <t>Tuopu Group</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>SSE:601689</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D10" s="52" t="n">
+        <v>195</v>
+      </c>
+      <c r="E10" s="52" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F10" s="52" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="G10" s="52" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H10" s="53" t="n">
+        <v>100</v>
+      </c>
+      <c r="I10" s="53" t="n">
+        <v>50</v>
+      </c>
+      <c r="J10" s="53" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="K10" s="53" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L10" s="54" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="51" t="inlineStr">
+        <is>
+          <t>Shuanglin</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>SZSE:300100</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D11" s="52" t="n">
+        <v>35</v>
+      </c>
+      <c r="E11" s="52" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="F11" s="52" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G11" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H11" s="53" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="I11" s="53" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="J11" s="53" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="K11" s="53" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L11" s="54" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="51" t="inlineStr">
+        <is>
+          <t>NSK (Japan)</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>TYO:6471</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D12" s="52" t="n">
+        <v>35</v>
+      </c>
+      <c r="E12" s="52" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="F12" s="52" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G12" s="52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H12" s="53" t="n">
+        <v>25</v>
+      </c>
+      <c r="I12" s="53" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J12" s="53" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K12" s="53" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L12" s="54" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>PEER STATISTICAL SUMMARY (excl. Hengli)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="H16" s="55">
+        <f>MAX(H5:H12)</f>
+        <v/>
+      </c>
+      <c r="I16" s="55">
+        <f>MAX(I5:I12)</f>
+        <v/>
+      </c>
+      <c r="J16" s="55">
+        <f>MAX(J5:J12)</f>
+        <v/>
+      </c>
+      <c r="K16" s="55">
+        <f>MAX(K5:K12)</f>
+        <v/>
+      </c>
+      <c r="L16" s="56">
+        <f>MAX(L5:L12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>75th percentile</t>
+        </is>
+      </c>
+      <c r="H17" s="55">
+        <f>PERCENTILE(H5:H12,0.75)</f>
+        <v/>
+      </c>
+      <c r="I17" s="55">
+        <f>PERCENTILE(I5:I12,0.75)</f>
+        <v/>
+      </c>
+      <c r="J17" s="55">
+        <f>PERCENTILE(J5:J12,0.75)</f>
+        <v/>
+      </c>
+      <c r="K17" s="55">
+        <f>PERCENTILE(K5:K12,0.75)</f>
+        <v/>
+      </c>
+      <c r="L17" s="56">
+        <f>PERCENTILE(L5:L12,0.75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="H18" s="55">
+        <f>MEDIAN(H5:H12)</f>
+        <v/>
+      </c>
+      <c r="I18" s="55">
+        <f>MEDIAN(I5:I12)</f>
+        <v/>
+      </c>
+      <c r="J18" s="55">
+        <f>MEDIAN(J5:J12)</f>
+        <v/>
+      </c>
+      <c r="K18" s="55">
+        <f>MEDIAN(K5:K12)</f>
+        <v/>
+      </c>
+      <c r="L18" s="56">
+        <f>MEDIAN(L5:L12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Mean</t>
+        </is>
+      </c>
+      <c r="H19" s="55">
+        <f>AVERAGE(H5:H12)</f>
+        <v/>
+      </c>
+      <c r="I19" s="55">
+        <f>AVERAGE(I5:I12)</f>
+        <v/>
+      </c>
+      <c r="J19" s="55">
+        <f>AVERAGE(J5:J12)</f>
+        <v/>
+      </c>
+      <c r="K19" s="55">
+        <f>AVERAGE(K5:K12)</f>
+        <v/>
+      </c>
+      <c r="L19" s="56">
+        <f>AVERAGE(L5:L12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>25th percentile</t>
+        </is>
+      </c>
+      <c r="H20" s="55">
+        <f>PERCENTILE(H5:H12,0.25)</f>
+        <v/>
+      </c>
+      <c r="I20" s="55">
+        <f>PERCENTILE(I5:I12,0.25)</f>
+        <v/>
+      </c>
+      <c r="J20" s="55">
+        <f>PERCENTILE(J5:J12,0.25)</f>
+        <v/>
+      </c>
+      <c r="K20" s="55">
+        <f>PERCENTILE(K5:K12,0.25)</f>
+        <v/>
+      </c>
+      <c r="L20" s="56">
+        <f>PERCENTILE(L5:L12,0.25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="H21" s="55">
+        <f>MIN(H5:H12)</f>
+        <v/>
+      </c>
+      <c r="I21" s="55">
+        <f>MIN(I5:I12)</f>
+        <v/>
+      </c>
+      <c r="J21" s="55">
+        <f>MIN(J5:J12)</f>
+        <v/>
+      </c>
+      <c r="K21" s="55">
+        <f>MIN(K5:K12)</f>
+        <v/>
+      </c>
+      <c r="L21" s="56">
+        <f>MIN(L5:L12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>HENGLI vs PEER MEDIAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Premium/(discount) to peer median %</t>
+        </is>
+      </c>
+      <c r="H24" s="10">
+        <f>H4/H20-1</f>
+        <v/>
+      </c>
+      <c r="I24" s="10">
+        <f>I4/I20-1</f>
+        <v/>
+      </c>
+      <c r="J24" s="10">
+        <f>J4/J20-1</f>
+        <v/>
+      </c>
+      <c r="K24" s="10">
+        <f>K4/K20-1</f>
+        <v/>
+      </c>
+      <c r="L24" s="10">
+        <f>L4/L20-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>IMPLIED PRICE PER SHARE (RMB) using peer median × FY2026E EPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Hengli FY2026E EPS (from Income Statement!H55)</t>
+        </is>
+      </c>
+      <c r="B27" s="57">
+        <f>'Income Statement'!H55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>× Peer median P/E</t>
+        </is>
+      </c>
+      <c r="B28" s="58">
+        <f>H20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>→ Implied price (P/E method)</t>
+        </is>
+      </c>
+      <c r="B29" s="59">
+        <f>B27*B28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  × Premium for humanoid optionality (1.20×)</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>→ Implied price w/ narrative premium</t>
+        </is>
+      </c>
+      <c r="B31" s="59">
+        <f>B29*B30</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A15:L15"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A23:L23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>HENGLI HYDRAULICS — VALUATION SUMMARY &amp; PRICE TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT SNAPSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Current price (RMB)</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="n">
+        <v>119.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Shares outstanding (million)</t>
+        </is>
+      </c>
+      <c r="B5" s="60" t="n">
+        <v>1340.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Market capitalization (RMB bn)</t>
+        </is>
+      </c>
+      <c r="B6" s="52" t="n">
+        <v>160.32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Net cash &amp; equivalents (RMB bn)</t>
+        </is>
+      </c>
+      <c r="B7" s="52" t="n">
+        <v>9.119999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Enterprise value (RMB bn)</t>
+        </is>
+      </c>
+      <c r="B8" s="52" t="n">
+        <v>151.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FY2025A revenue (RMB bn)</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="n">
+        <v>10.94</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FY2025A net income (RMB bn)</t>
+        </is>
+      </c>
+      <c r="B10" s="52" t="n">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TTM P/E (×)</t>
+        </is>
+      </c>
+      <c r="B11" s="53" t="n">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TTM EV/EBITDA (×)</t>
+        </is>
+      </c>
+      <c r="B12" s="53" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TTM P/S (×)</t>
+        </is>
+      </c>
+      <c r="B13" s="53" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P/B (×)</t>
+        </is>
+      </c>
+      <c r="B14" s="53" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ROE FY2025A (%)</t>
+        </is>
+      </c>
+      <c r="B15" s="54" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>FOOTBALL FIELD — Implied price per share (RMB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Methodology</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Weighted mid</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DCF — Base case (WACC 8.5%, g 3.0%)</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="n">
+        <v>62</v>
+      </c>
+      <c r="C20" s="20" t="n">
+        <v>77</v>
+      </c>
+      <c r="D20" s="20" t="n">
+        <v>95</v>
+      </c>
+      <c r="E20" s="61" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F20" s="19">
+        <f>C20*E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DCF — Bull/Bear range</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="C21" s="20" t="n">
+        <v>77</v>
+      </c>
+      <c r="D21" s="20" t="n">
+        <v>135</v>
+      </c>
+      <c r="E21" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="19">
+        <f>C21*E21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P/E — Peer median × FY26E EPS</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="n">
+        <v>75</v>
+      </c>
+      <c r="C22" s="20" t="n">
+        <v>102</v>
+      </c>
+      <c r="D22" s="20" t="n">
+        <v>130</v>
+      </c>
+      <c r="E22" s="61" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F22" s="19">
+        <f>C22*E22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P/E — 'Humanoid' premium (1.2× peer)</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="C23" s="20" t="n">
+        <v>122</v>
+      </c>
+      <c r="D23" s="20" t="n">
+        <v>156</v>
+      </c>
+      <c r="E23" s="61" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F23" s="19">
+        <f>C23*E23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EV/EBITDA — Peer median × FY26E EBITDA</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="C24" s="20" t="n">
+        <v>98</v>
+      </c>
+      <c r="D24" s="20" t="n">
+        <v>132</v>
+      </c>
+      <c r="E24" s="61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F24" s="19">
+        <f>C24*E24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P/B — Peer median × FY26E book</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="n">
+        <v>85</v>
+      </c>
+      <c r="C25" s="20" t="n">
+        <v>115</v>
+      </c>
+      <c r="D25" s="20" t="n">
+        <v>150</v>
+      </c>
+      <c r="E25" s="61" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F25" s="19">
+        <f>C25*E25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Precedent — humanoid supply-chain re-rating</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="n">
+        <v>110</v>
+      </c>
+      <c r="C26" s="20" t="n">
+        <v>145</v>
+      </c>
+      <c r="D26" s="20" t="n">
+        <v>200</v>
+      </c>
+      <c r="E26" s="61" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F26" s="19">
+        <f>C26*E26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>52-week trading range</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n">
+        <v>80</v>
+      </c>
+      <c r="C27" s="20" t="n">
+        <v>115</v>
+      </c>
+      <c r="D27" s="20" t="n">
+        <v>142</v>
+      </c>
+      <c r="E27" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="19">
+        <f>C27*E27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>12-MONTH PRICE TARGET (weighted average)</t>
+        </is>
+      </c>
+      <c r="F29" s="62">
+        <f>SUM(F20:F27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Weights sum check</t>
+        </is>
+      </c>
+      <c r="E30" s="63">
+        <f>SUM(E20:E27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Current price</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="n">
+        <v>119.6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>12-month price target</t>
+        </is>
+      </c>
+      <c r="B33" s="18">
+        <f>F29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Implied upside</t>
+        </is>
+      </c>
+      <c r="B34" s="35">
+        <f>B33/B32-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION</t>
+        </is>
+      </c>
+      <c r="B36" s="65" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>KEY CATALYSTS (next 12 months)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>1. Linear-drive (planetary roller-screw) revenue &gt;RMB 300m in FY2026 — mgmt guidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>2. Hengli announced as Tier-1 supplier for any Tesla Optimus, Figure, or Chinese humanoid Tier-1 program (probability-weighted ~25%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>3. Mexico plant Caterpillar Tier-1 ramp to &gt;USD 300m run-rate by end of FY2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>4. Mid-large excavator industry up-cycle inflection — China industry shipments expected to grow 12-15% in 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>5. Continued domestic gross-margin recovery on Bosch Rexroth retreat from low-end Chinese OEMs</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>KEY RISKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>1. Linear-drive execution risk — RMB 1.4bn invested, only ~RMB 100m FY25 revenue at 15% GM vs 41% group GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>2. Caterpillar in-sourcing — Mexicali plant could cut Hengli cylinder share from ~80% to &lt;50% (~RMB 500-700m risk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>3. Excavator cyclical down-cycle return 2027-2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>4. Humanoid premium derating — TTM P/E 58× already in top decile of 3y band; sentiment-driven multiple compression risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>5. RMB / USD / EUR FX hedging risk on USD 580m notional swap book</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A43:F43"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -773,7 +2159,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -2368,7 +3754,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L59"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -4500,7 +5886,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -5470,7 +6856,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L68"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -7547,7 +8933,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -7938,7 +9324,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -8221,9 +9607,6 @@
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-    </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
@@ -8364,4 +9747,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>HENGLI HYDRAULICS — DCF VALUATION (Base case, RMB millions)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>FY2026E</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>FY2027E</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>FY2028E</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>FY2029E</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>FY2030E</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Unlevered Free Cash Flow (UFCF)</t>
+        </is>
+      </c>
+      <c r="B5" s="15">
+        <f>'DCF Inputs'!B12</f>
+        <v/>
+      </c>
+      <c r="C5" s="15">
+        <f>'DCF Inputs'!C12</f>
+        <v/>
+      </c>
+      <c r="D5" s="15">
+        <f>'DCF Inputs'!D12</f>
+        <v/>
+      </c>
+      <c r="E5" s="15">
+        <f>'DCF Inputs'!E12</f>
+        <v/>
+      </c>
+      <c r="F5" s="15">
+        <f>'DCF Inputs'!F12</f>
+        <v/>
+      </c>
+      <c r="G5" s="11">
+        <f>F5*(1+B12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Discount period (mid-year convention)</t>
+        </is>
+      </c>
+      <c r="B6" s="39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C6" s="39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E6" s="39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F6" s="39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G6" s="39" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Discount factor (1/(1+WACC)^t)</t>
+        </is>
+      </c>
+      <c r="B7" s="40">
+        <f>1/(1+$B$17)^B6</f>
+        <v/>
+      </c>
+      <c r="C7" s="40">
+        <f>1/(1+$B$17)^C6</f>
+        <v/>
+      </c>
+      <c r="D7" s="40">
+        <f>1/(1+$B$17)^D6</f>
+        <v/>
+      </c>
+      <c r="E7" s="40">
+        <f>1/(1+$B$17)^E6</f>
+        <v/>
+      </c>
+      <c r="F7" s="40">
+        <f>1/(1+$B$17)^F6</f>
+        <v/>
+      </c>
+      <c r="G7" s="40">
+        <f>1/(1+$B$17)^G6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PV of UFCF</t>
+        </is>
+      </c>
+      <c r="B8" s="34">
+        <f>B5*B7</f>
+        <v/>
+      </c>
+      <c r="C8" s="34">
+        <f>C5*C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="34">
+        <f>D5*D7</f>
+        <v/>
+      </c>
+      <c r="E8" s="34">
+        <f>E5*E7</f>
+        <v/>
+      </c>
+      <c r="F8" s="34">
+        <f>F5*F7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>TERMINAL VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Terminal UFCF (FY2031E)</t>
+        </is>
+      </c>
+      <c r="B11" s="15">
+        <f>G5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Terminal growth rate (g)</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Terminal value (Gordon: UFCF / (WACC-g))</t>
+        </is>
+      </c>
+      <c r="B13" s="34">
+        <f>B11/(B17-B12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PV of terminal value (× DF Year 5)</t>
+        </is>
+      </c>
+      <c r="B14" s="34">
+        <f>B13*G7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Terminal value as % of EV</t>
+        </is>
+      </c>
+      <c r="B15" s="41">
+        <f>B14/(SUM(B8:F8)+B14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>WACC (input from DCF Inputs tab)</t>
+        </is>
+      </c>
+      <c r="B17" s="42">
+        <f>'DCF Inputs'!B30</f>
+        <v/>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Sourced from DCF Inputs!B30 (WACC build)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>ENTERPRISE VALUE BUILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sum of PV of UFCF (Year 1-5)</t>
+        </is>
+      </c>
+      <c r="B20" s="11">
+        <f>SUM(B8:F8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  + PV of terminal value</t>
+        </is>
+      </c>
+      <c r="B21" s="11">
+        <f>B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>→ ENTERPRISE VALUE</t>
+        </is>
+      </c>
+      <c r="B22" s="23">
+        <f>B20+B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    + Net cash &amp; equivalents (FY25 cash 8,871 + trading FA 345)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>9216</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    − Total debt (ST 14 + LT 20)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>-34</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    − Minority interest</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>-58</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>→ EQUITY VALUE</t>
+        </is>
+      </c>
+      <c r="B26" s="23">
+        <f>B22+9216-34-58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ÷ Shares outstanding (million)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>1340.8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>→ DCF IMPLIED PRICE PER SHARE (RMB)</t>
+        </is>
+      </c>
+      <c r="B28" s="43">
+        <f>B26/B27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Current price (May 2026)</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="n">
+        <v>119.6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>DCF upside/(downside) %</t>
+        </is>
+      </c>
+      <c r="B31" s="35">
+        <f>B28/B30-1</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>DCF SENSITIVITY ANALYSIS — Implied price per share (RMB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Terminal growth (g) →</t>
+        </is>
+      </c>
+      <c r="B3" s="44" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C3" s="44" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D3" s="44" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E3" s="44" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="F3" s="44" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="44" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="B4" s="19" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="C4" s="19" t="n">
+        <v>74.63</v>
+      </c>
+      <c r="D4" s="19" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="E4" s="19" t="n">
+        <v>89.42</v>
+      </c>
+      <c r="F4" s="19" t="n">
+        <v>99.98</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="44" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>63.76</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>68.16</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>73.44</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>79.89</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>87.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="44" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="B6" s="19" t="n">
+        <v>59.11</v>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>62.77</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>67.09</v>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>72.27</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>78.59999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="44" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>55.14</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>58.21</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>66.04000000000001</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>71.13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="44" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="B8" s="19" t="n">
+        <v>51.69</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>54.31</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>60.85</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>65.02</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>48.69</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>50.93</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>59.93</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Current price (May 2026):</t>
+        </is>
+      </c>
+      <c r="B12" s="45" t="n">
+        <v>119.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Base case (WACC 8.5%, g 3.0%) →</t>
+        </is>
+      </c>
+      <c r="B13" s="18">
+        <f>D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Highlighted cells indicate combinations with implied price &gt; current.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B4:F9">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>